--- a/artfynd/A 40273-2024 artfynd.xlsx
+++ b/artfynd/A 40273-2024 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>119799461</v>
       </c>
       <c r="B6" t="n">
-        <v>91254</v>
+        <v>91272</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
